--- a/Documentation/Purchased Parts BOM.xlsx
+++ b/Documentation/Purchased Parts BOM.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Arcade-Project\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Arcade-Project\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0BA965-E2BA-4C5D-BF2D-1AC3E39326E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20325" windowHeight="7080"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts and Materials" sheetId="1" r:id="rId1"/>
     <sheet name="Tools" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parts and Materials'!$A$1:$E$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parts and Materials'!$A$1:$E$63</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
   <si>
     <t>80mm Fan Grill</t>
   </si>
@@ -66,12 +67,6 @@
     <t>MH-16A</t>
   </si>
   <si>
-    <t>White LEDs for Marquee 2' strips</t>
-  </si>
-  <si>
-    <t>TGWC-F84-12V</t>
-  </si>
-  <si>
     <t>Wired DHT22 temperature-humidity sensor</t>
   </si>
   <si>
@@ -514,13 +509,31 @@
   </si>
   <si>
     <t>Raspberry Pi Parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	CA-KN3D-123</t>
+  </si>
+  <si>
+    <t>Momentary Toggle Switch 12V 25A SPDT (ON)/Off/(ON) 3 pin</t>
+  </si>
+  <si>
+    <t>2-6-26 - Added this item to work with the 3D printed 2 switch version</t>
+  </si>
+  <si>
+    <t>These parts are end of life, a replacemnt needs to be identified</t>
+  </si>
+  <si>
+    <t>5V-DIMMABLE</t>
+  </si>
+  <si>
+    <t>White LEDs for Marquee 2' strips 5V Dimmable (3 Pin, PWM controlled)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,8 +569,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -570,8 +591,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -603,11 +642,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -645,15 +694,23 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -931,8 +988,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E76"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="13" bestFit="1" customWidth="1"/>
@@ -940,24 +997,25 @@
     <col min="3" max="3" width="88.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="12"/>
+    <col min="6" max="6" width="63.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -965,13 +1023,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -980,16 +1038,16 @@
         <v>50</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -997,16 +1055,16 @@
         <v>50</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1014,16 +1072,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1034,13 +1092,13 @@
         <v>4356</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1048,16 +1106,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1071,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -1083,10 +1141,10 @@
         <v>8541607606</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -1098,10 +1156,10 @@
         <v>4330172261</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" s="6"/>
     </row>
@@ -1116,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="6"/>
     </row>
@@ -1125,13 +1183,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" s="6"/>
     </row>
@@ -1140,16 +1198,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1157,13 +1215,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" s="6"/>
     </row>
@@ -1172,13 +1230,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="6"/>
     </row>
@@ -1187,13 +1245,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="6"/>
     </row>
@@ -1208,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="6"/>
     </row>
@@ -1223,10 +1281,10 @@
         <v>10</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1240,7 +1298,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="6"/>
     </row>
@@ -1249,13 +1307,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" s="6"/>
     </row>
@@ -1264,16 +1322,16 @@
         <v>1</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1281,16 +1339,16 @@
         <v>10</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1301,13 +1359,13 @@
         <v>9508080</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1318,13 +1376,13 @@
         <v>9508021</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1335,13 +1393,13 @@
         <v>9508031</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1352,13 +1410,13 @@
         <v>9508041</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1369,13 +1427,13 @@
         <v>8500106</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1383,16 +1441,16 @@
         <v>1</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1403,10 +1461,10 @@
         <v>9</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E29" s="6"/>
     </row>
@@ -1415,13 +1473,13 @@
         <v>8</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E30" s="6"/>
     </row>
@@ -1430,13 +1488,13 @@
         <v>8</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E31" s="6"/>
     </row>
@@ -1445,47 +1503,47 @@
         <v>8</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="E32" s="6"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>1</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>1</v>
       </c>
@@ -1493,14 +1551,14 @@
         <v>5597</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35" s="6"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>1</v>
       </c>
@@ -1508,44 +1566,44 @@
         <v>3992</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>1</v>
       </c>
       <c r="B37" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="D38" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>2</v>
       </c>
@@ -1553,14 +1611,14 @@
         <v>7233</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>1</v>
       </c>
@@ -1568,14 +1626,14 @@
         <v>33560</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>1</v>
       </c>
@@ -1583,133 +1641,139 @@
         <v>33566</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
         <v>3</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
+        <v>3</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="22"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
+        <v>3</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="8" t="s">
+      <c r="D44" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F44" s="22"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
+        <v>25</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>3</v>
-      </c>
-      <c r="B43" s="7" t="s">
+      <c r="D45" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>3</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>25</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F45" s="22"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>3</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>2</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>2</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>1</v>
       </c>
@@ -1717,16 +1781,16 @@
         <v>3221386</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>1</v>
       </c>
@@ -1734,16 +1798,16 @@
         <v>3221386</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>6</v>
       </c>
@@ -1751,16 +1815,16 @@
         <v>2751150</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>12</v>
       </c>
@@ -1768,211 +1832,214 @@
         <v>2751148</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>1</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>1</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>3</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>1</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>80</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>2</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>3</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>161</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E60" s="6"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="6"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
-        <v>1</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>56</v>
-      </c>
+      <c r="F60" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>1</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="6"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="8"/>
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>1</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>121</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>1</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E65" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>1</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E66" s="6"/>
     </row>
@@ -1980,14 +2047,14 @@
       <c r="A67" s="6">
         <v>1</v>
       </c>
-      <c r="B67" s="7">
-        <v>8541602182</v>
+      <c r="B67" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E67" s="6"/>
     </row>
@@ -1995,14 +2062,14 @@
       <c r="A68" s="6">
         <v>1</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>154</v>
+      <c r="B68" s="7">
+        <v>8541602182</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E68" s="6"/>
     </row>
@@ -2011,13 +2078,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E69" s="6"/>
     </row>
@@ -2026,13 +2093,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E70" s="6"/>
     </row>
@@ -2041,38 +2108,38 @@
         <v>1</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E71" s="6"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D73" s="8"/>
-      <c r="E73" s="6"/>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>1</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" s="6"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>1</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="A74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" s="8"/>
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,44 +2147,65 @@
         <v>1</v>
       </c>
       <c r="B75" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="6"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>1</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" s="6"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="17">
-        <v>1</v>
-      </c>
-      <c r="B76" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>159</v>
-      </c>
       <c r="D76" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E76" s="17"/>
+        <v>112</v>
+      </c>
+      <c r="E76" s="6"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>1</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" t="s">
+        <v>157</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E77" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E62"/>
-  <sortState ref="A2:E67">
-    <sortCondition ref="D2:D67"/>
-    <sortCondition ref="C2:C67"/>
+  <autoFilter ref="A1:E63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E68">
+    <sortCondition ref="D2:D68"/>
+    <sortCondition ref="C2:C68"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="F42:F45"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C60" r:id="rId1" xr:uid="{86BF16C3-0908-4841-AE43-62BF18CFB0F4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2129,16 +2217,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2146,13 +2234,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2160,13 +2248,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2174,13 +2262,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2188,13 +2276,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2202,13 +2290,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,13 +2304,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2230,13 +2318,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2244,13 +2332,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2258,13 +2346,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,13 +2360,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
         <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
